--- a/output/pdf_financials_xlsx/GOLD.xlsx
+++ b/output/pdf_financials_xlsx/GOLD.xlsx
@@ -4704,43 +4704,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.127199</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.191336</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.56976</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.790267</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.034813</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>8.463455</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>9.248583999999999</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>9.939966</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.107</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>11.93</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>13.493</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>14.05</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>14.786</v>
       </c>
     </row>
     <row r="93">
@@ -8831,7 +8831,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -10195,7 +10199,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -11279,7 +11287,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -13068,7 +13080,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -15187,7 +15203,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
         <v>1.127199</v>
       </c>

--- a/output/pdf_financials_xlsx/GOLD.xlsx
+++ b/output/pdf_financials_xlsx/GOLD.xlsx
@@ -917,43 +917,43 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.100624</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.031534</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.027969</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.02408</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.052218</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.201056</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.188833</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.155298</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.657</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="13">
@@ -1659,43 +1659,43 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.537369</v>
+        <v>-4.637993</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.502012</v>
+        <v>-5.533546</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.049042</v>
+        <v>-5.077011</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.215507</v>
+        <v>-4.239587</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.536983</v>
+        <v>-7.589201</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-7.727143</v>
+        <v>-7.928199</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.596404</v>
+        <v>-6.785237</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-6.215974</v>
+        <v>-6.371272</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>100.184</v>
+        <v>100.176</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-13.211</v>
+        <v>-13.264</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-35.349</v>
+        <v>-36.006</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-29.279</v>
+        <v>-29.989</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-15.332</v>
+        <v>-15.646</v>
       </c>
     </row>
     <row r="28">
@@ -1751,43 +1751,43 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.515147</v>
+        <v>-4.615771</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.46101</v>
+        <v>-5.492544</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.98653</v>
+        <v>-5.014499</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.10702</v>
+        <v>-4.1311</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.3004</v>
+        <v>-7.352618</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-7.438402</v>
+        <v>-7.639458</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.325836</v>
+        <v>-6.514669</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.002562</v>
+        <v>-6.15786</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>100.37</v>
+        <v>100.362</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-13.001</v>
+        <v>-13.054</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-35.147</v>
+        <v>-35.804</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-28.948</v>
+        <v>-29.658</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-14.986</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="30">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.520141</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.225827</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.798512</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.445056</v>
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.520141</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.225827</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.798512</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.445056</v>
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.677702</v>
+        <v>0.157561</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.32469</v>
+        <v>0.09886300000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.923104</v>
+        <v>0.124592</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.081653</v>
@@ -7416,7 +7416,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -10578,7 +10582,11 @@
           <t>Reclamation deposits 11</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -12644,7 +12652,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -14103,7 +14115,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -14585,7 +14597,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -19083,7 +19095,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -25408,7 +25424,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" s="5" t="n">
@@ -35896,7 +35912,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">

--- a/output/pdf_financials_xlsx/GOLD.xlsx
+++ b/output/pdf_financials_xlsx/GOLD.xlsx
@@ -1125,7 +1125,7 @@
         <v>-6.215974</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>100.184</v>
+        <v>91.173</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-13.211</v>
@@ -1137,7 +1137,7 @@
         <v>-29.279</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-15.332</v>
+        <v>-15.093</v>
       </c>
     </row>
     <row r="17">
@@ -1171,7 +1171,7 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>9.010999999999999</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0.011</v>
@@ -1183,7 +1183,7 @@
         <v>1.932</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.239</v>
       </c>
     </row>
     <row r="18">
@@ -1683,7 +1683,7 @@
         <v>-6.371272</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>100.176</v>
+        <v>91.16500000000001</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-13.264</v>
@@ -1695,7 +1695,7 @@
         <v>-29.989</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-15.646</v>
+        <v>-15.407</v>
       </c>
     </row>
     <row r="28">
@@ -1775,7 +1775,7 @@
         <v>-6.15786</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>100.362</v>
+        <v>91.351</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-13.054</v>
@@ -1787,7 +1787,7 @@
         <v>-29.658</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-15.3</v>
+        <v>-15.061</v>
       </c>
     </row>
     <row r="30">
@@ -1893,7 +1893,7 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>9.88340846522545</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0.08326394671107411</v>
@@ -1905,7 +1905,7 @@
         <v>-6.598586017282011</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.583515537003909</v>
       </c>
     </row>
     <row r="32">
@@ -3400,13 +3400,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.171186</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.975125</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.952526</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
@@ -3538,25 +3538,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.08006099999999999</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.11246</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.085213</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.076112</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.134984</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.09191299999999999</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.222651</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -3700,19 +3700,19 @@
         <v>0</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="71">
@@ -3746,19 +3746,19 @@
         <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>12.482</v>
+        <v>12.536</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>8.824</v>
+        <v>8.914</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="72">
@@ -3930,19 +3930,19 @@
         <v>0.178241</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.1</v>
+        <v>0.046</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.444</v>
+        <v>0.354</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.587</v>
+        <v>0.521</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2.633</v>
+        <v>2.545</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.739</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="76">
@@ -4176,19 +4176,19 @@
         </is>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.06271139866603383</v>
+        <v>0.062981189578077</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.06651812481956607</v>
+        <v>0.06718434240622988</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.002426557901801848</v>
+        <v>0.002913344593348723</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.002565136449816837</v>
+        <v>0.00332009299692012</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.0008562638497450571</v>
+        <v>0.001286547191325488</v>
       </c>
     </row>
     <row r="81">
@@ -5502,31 +5502,31 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.002189</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.007025</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.008940999999999999</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.014133</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.019863</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019536</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016454</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -5563,16 +5563,16 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -6679,10 +6679,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019536</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016454</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -6703,16 +6703,16 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-4.194408</v>
+        <v>-4.213944</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-4.834212</v>
+        <v>-4.850666</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-4.86384</v>
@@ -6749,16 +6749,16 @@
         <v>-4.623985</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-7.915</v>
+        <v>-7.922</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-10.986</v>
+        <v>-11.021</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-21.832</v>
+        <v>-22.002</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-22.528</v>
+        <v>-22.771</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-23.218</v>
@@ -8164,7 +8164,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -15805,7 +15809,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -17056,7 +17064,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E135" s="5" t="n">
         <v>-0.019536</v>
       </c>
@@ -18173,7 +18185,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -18631,7 +18647,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -21177,7 +21197,11 @@
           <t>Proceeds from GRC private placement</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -21984,10 +22008,8 @@
       <c r="J198" s="5" t="n">
         <v>-7.727143</v>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K198" s="5" t="n">
+        <v>-6.596404</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -22028,12 +22050,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Adjustments for items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Loss on disposal of equipment</t>
+          <t>Proceeds from shares and warrants issued, net of issuance costs</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -22047,28 +22069,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G199" s="5" t="n">
+        <v>6.10923</v>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>4.276088</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>0.005875</v>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.627283</v>
+      </c>
+      <c r="J199" s="5" t="n">
+        <v>0.54047</v>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>1.071842</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -22114,7 +22128,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Proceeds from shares and warrants issued, net of issuance costs</t>
+          <t>Advances from related parties</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -22123,27 +22137,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F200" s="5" t="n">
+        <v>-0.001893</v>
       </c>
       <c r="G200" s="5" t="n">
-        <v>6.10923</v>
+        <v>0.019229</v>
       </c>
       <c r="H200" s="5" t="n">
-        <v>4.276088</v>
+        <v>-0.020885</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>25.627283</v>
+        <v>0.003026</v>
       </c>
       <c r="J200" s="5" t="n">
-        <v>0.54047</v>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006357</v>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>-0.008815999999999999</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -22184,12 +22194,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Settlement of long-term obligations</t>
+          <t>Beginning of period</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -22214,17 +22224,13 @@
         </is>
       </c>
       <c r="I201" s="5" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.445056</v>
+      </c>
+      <c r="J201" s="5" t="n">
+        <v>21.338388</v>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>13.9611</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -22265,12 +22271,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Advances from joint venture</t>
+          <t>End of period</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -22295,17 +22301,13 @@
         </is>
       </c>
       <c r="I202" s="5" t="n">
-        <v>0.043288</v>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.338388</v>
+      </c>
+      <c r="J202" s="5" t="n">
+        <v>13.9611</v>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>9.644214</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -22346,12 +22348,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for items not involving cash</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Advances from related parties</t>
+          <t>Loss on disposal of equipment</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -22360,20 +22362,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F203" s="5" t="n">
-        <v>-0.001893</v>
-      </c>
-      <c r="G203" s="5" t="n">
-        <v>0.019229</v>
-      </c>
-      <c r="H203" s="5" t="n">
-        <v>-0.020885</v>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I203" s="5" t="n">
-        <v>0.003026</v>
-      </c>
-      <c r="J203" s="5" t="n">
-        <v>0.006357</v>
+        <v>0.005875</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -22419,12 +22429,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Beginning of period</t>
+          <t>Settlement of long-term obligations</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -22449,10 +22459,12 @@
         </is>
       </c>
       <c r="I204" s="5" t="n">
-        <v>1.445056</v>
-      </c>
-      <c r="J204" s="5" t="n">
-        <v>21.338388</v>
+        <v>-0.3</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -22498,12 +22510,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>End of period</t>
+          <t>Advances from joint venture</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -22528,10 +22540,12 @@
         </is>
       </c>
       <c r="I205" s="5" t="n">
-        <v>21.338388</v>
-      </c>
-      <c r="J205" s="5" t="n">
-        <v>13.9611</v>
+        <v>0.043288</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -25963,7 +25977,11 @@
           <t>Current income tax recovery (expense) 15</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -26042,7 +26060,11 @@
           <t>Deferred income tax recovery (expense) 15</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -30265,7 +30287,11 @@
           <t>Deferred income tax recovery (expense) 16</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -31768,7 +31794,11 @@
           <t>Deferred income tax recovery (expense) 14</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
